--- a/backend/data/financials_by_company/1269.HK.xlsx
+++ b/backend/data/financials_by_company/1269.HK.xlsx
@@ -687,630 +687,630 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-1163318.233972</v>
+        <v>-1242139.076691</v>
       </c>
       <c r="C2" t="n">
-        <v>0.029982</v>
+        <v>0.001928</v>
       </c>
       <c r="D2" t="n">
-        <v>-139675000</v>
+        <v>-244470000</v>
       </c>
       <c r="E2" t="n">
-        <v>-38800000</v>
+        <v>-369059000</v>
       </c>
       <c r="F2" t="n">
-        <v>-38800000</v>
+        <v>-644162000</v>
       </c>
       <c r="G2" t="n">
-        <v>-393183000</v>
+        <v>-751317000</v>
       </c>
       <c r="H2" t="n">
-        <v>72913000</v>
+        <v>76335000</v>
       </c>
       <c r="I2" t="n">
-        <v>1844587000</v>
+        <v>923539000</v>
       </c>
       <c r="J2" t="n">
-        <v>-178475000</v>
+        <v>-613529000</v>
       </c>
       <c r="K2" t="n">
-        <v>-251388000</v>
+        <v>-689864000</v>
       </c>
       <c r="L2" t="n">
-        <v>-230823000</v>
+        <v>-176439000</v>
       </c>
       <c r="M2" t="n">
-        <v>234063000</v>
+        <v>197445000</v>
       </c>
       <c r="N2" t="n">
-        <v>3240000</v>
+        <v>21006000</v>
       </c>
       <c r="O2" t="n">
-        <v>-355546318.233972</v>
+        <v>166705860.923309</v>
       </c>
       <c r="P2" t="n">
-        <v>-393183000</v>
+        <v>-968233000</v>
       </c>
       <c r="Q2" t="n">
-        <v>2404952000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>3313000</v>
-      </c>
+        <v>1217407000</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>-218980000</v>
+        <v>-502642000</v>
       </c>
       <c r="T2" t="n">
-        <v>1848000000</v>
+        <v>1097308462</v>
       </c>
       <c r="U2" t="n">
-        <v>1848000000</v>
+        <v>1097308462</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
+        <v>-0.88</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-0.88</v>
+      </c>
       <c r="X2" t="n">
-        <v>-393183000</v>
+        <v>-968233000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-393183000</v>
+        <v>-968233000</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-393183000</v>
+        <v>-968233000</v>
       </c>
       <c r="AB2" t="n">
-        <v>77713000</v>
+        <v>134281000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-470896000</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
+        <v>-1102514000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>-216916000</v>
+      </c>
       <c r="AE2" t="n">
-        <v>-470896000</v>
+        <v>-885598000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-14555000</v>
+        <v>-1711000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-485451000</v>
+        <v>-887309000</v>
       </c>
       <c r="AH2" t="n">
-        <v>46963000</v>
+        <v>-16203000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-4616000</v>
+        <v>-471676000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-3672000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>-10694000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>103267000</v>
+      </c>
       <c r="AL2" t="n">
-        <v>8288000</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
+        <v>104000000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
       <c r="AN2" t="n">
-        <v>-230823000</v>
+        <v>-176439000</v>
       </c>
       <c r="AO2" t="n">
-        <v>234063000</v>
+        <v>197445000</v>
       </c>
       <c r="AP2" t="n">
-        <v>3240000</v>
+        <v>21006000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-217736000</v>
+        <v>-123577000</v>
       </c>
       <c r="AR2" t="n">
-        <v>560365000</v>
+        <v>293868000</v>
       </c>
       <c r="AS2" t="n">
-        <v>182516000</v>
+        <v>18919000</v>
       </c>
       <c r="AT2" t="n">
-        <v>115723000</v>
+        <v>59903000</v>
       </c>
       <c r="AU2" t="n">
-        <v>290340000</v>
+        <v>252722000</v>
       </c>
       <c r="AV2" t="n">
-        <v>82375000</v>
+        <v>114636000</v>
       </c>
       <c r="AW2" t="n">
-        <v>207965000</v>
+        <v>138086000</v>
       </c>
       <c r="AX2" t="n">
-        <v>342629000</v>
+        <v>170291000</v>
       </c>
       <c r="AY2" t="n">
-        <v>1844587000</v>
+        <v>923539000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2187216000</v>
+        <v>1093830000</v>
       </c>
       <c r="BA2" t="n">
-        <v>2187216000</v>
+        <v>1093830000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-13543.385541</v>
+        <v>8802.621520000001</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000653</v>
+        <v>0.000793</v>
       </c>
       <c r="D3" t="n">
-        <v>-120315000</v>
+        <v>-163393000</v>
       </c>
       <c r="E3" t="n">
-        <v>-20753000</v>
+        <v>11100000</v>
       </c>
       <c r="F3" t="n">
-        <v>-20753000</v>
+        <v>11100000</v>
       </c>
       <c r="G3" t="n">
-        <v>-347172000</v>
+        <v>-420736000</v>
       </c>
       <c r="H3" t="n">
-        <v>64090000</v>
+        <v>69338000</v>
       </c>
       <c r="I3" t="n">
-        <v>1432595000</v>
+        <v>997802000</v>
       </c>
       <c r="J3" t="n">
-        <v>-141068000</v>
+        <v>-152293000</v>
       </c>
       <c r="K3" t="n">
-        <v>-205158000</v>
+        <v>-221631000</v>
       </c>
       <c r="L3" t="n">
-        <v>-149154000</v>
+        <v>-184598000</v>
       </c>
       <c r="M3" t="n">
-        <v>161070000</v>
+        <v>198278000</v>
       </c>
       <c r="N3" t="n">
-        <v>11916000</v>
+        <v>13680000</v>
       </c>
       <c r="O3" t="n">
-        <v>-326432543.385541</v>
+        <v>-431827197.37848</v>
       </c>
       <c r="P3" t="n">
-        <v>-347172000</v>
+        <v>-420736000</v>
       </c>
       <c r="Q3" t="n">
-        <v>1972393000</v>
+        <v>1251949000</v>
       </c>
       <c r="R3" t="n">
-        <v>1999000</v>
+        <v>794000</v>
       </c>
       <c r="S3" t="n">
-        <v>-116111000</v>
+        <v>-224056000</v>
       </c>
       <c r="T3" t="n">
-        <v>1791339452</v>
+        <v>1528231808</v>
       </c>
       <c r="U3" t="n">
-        <v>1791339452</v>
+        <v>1528231808</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.19</v>
+        <v>-0.28</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.19</v>
+        <v>-0.28</v>
       </c>
       <c r="X3" t="n">
-        <v>-347172000</v>
+        <v>-420736000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-347172000</v>
+        <v>-420736000</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-347172000</v>
+        <v>-420736000</v>
       </c>
       <c r="AB3" t="n">
-        <v>18817000</v>
+        <v>-1160000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-365989000</v>
-      </c>
-      <c r="AD3" t="inlineStr"/>
+        <v>-419576000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
       <c r="AE3" t="n">
-        <v>-365989000</v>
+        <v>-419576000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-239000</v>
+        <v>-333000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-366228000</v>
+        <v>-419909000</v>
       </c>
       <c r="AH3" t="n">
-        <v>25342000</v>
+        <v>19991000</v>
       </c>
       <c r="AI3" t="n">
-        <v>8070000</v>
+        <v>-27526000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-8070000</v>
+        <v>14664000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>12862000</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
-        <v>-149154000</v>
+        <v>-184598000</v>
       </c>
       <c r="AO3" t="n">
-        <v>161070000</v>
+        <v>198278000</v>
       </c>
       <c r="AP3" t="n">
-        <v>11916000</v>
+        <v>13680000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-138673000</v>
+        <v>-52037000</v>
       </c>
       <c r="AR3" t="n">
-        <v>539798000</v>
+        <v>254147000</v>
       </c>
       <c r="AS3" t="n">
-        <v>247476000</v>
+        <v>16192000</v>
       </c>
       <c r="AT3" t="n">
-        <v>104344000</v>
+        <v>64509000</v>
       </c>
       <c r="AU3" t="n">
-        <v>216816000</v>
+        <v>192119000</v>
       </c>
       <c r="AV3" t="n">
-        <v>62009000</v>
+        <v>55348000</v>
       </c>
       <c r="AW3" t="n">
-        <v>154807000</v>
+        <v>136771000</v>
       </c>
       <c r="AX3" t="n">
-        <v>401125000</v>
+        <v>202110000</v>
       </c>
       <c r="AY3" t="n">
-        <v>1432595000</v>
+        <v>997802000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1833720000</v>
+        <v>1199912000</v>
       </c>
       <c r="BA3" t="n">
-        <v>1833720000</v>
+        <v>1199912000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>8802.621520000001</v>
+        <v>-13543.385541</v>
       </c>
       <c r="C4" t="n">
-        <v>0.000793</v>
+        <v>0.000653</v>
       </c>
       <c r="D4" t="n">
-        <v>-163393000</v>
+        <v>-120315000</v>
       </c>
       <c r="E4" t="n">
-        <v>11100000</v>
+        <v>-20753000</v>
       </c>
       <c r="F4" t="n">
-        <v>11100000</v>
+        <v>-20753000</v>
       </c>
       <c r="G4" t="n">
-        <v>-420736000</v>
+        <v>-347172000</v>
       </c>
       <c r="H4" t="n">
-        <v>69338000</v>
+        <v>64090000</v>
       </c>
       <c r="I4" t="n">
-        <v>997802000</v>
+        <v>1432595000</v>
       </c>
       <c r="J4" t="n">
-        <v>-152293000</v>
+        <v>-141068000</v>
       </c>
       <c r="K4" t="n">
-        <v>-221631000</v>
+        <v>-205158000</v>
       </c>
       <c r="L4" t="n">
-        <v>-184598000</v>
+        <v>-149154000</v>
       </c>
       <c r="M4" t="n">
-        <v>198278000</v>
+        <v>161070000</v>
       </c>
       <c r="N4" t="n">
-        <v>13680000</v>
+        <v>11916000</v>
       </c>
       <c r="O4" t="n">
-        <v>-431827197.37848</v>
+        <v>-326432543.385541</v>
       </c>
       <c r="P4" t="n">
-        <v>-420736000</v>
+        <v>-347172000</v>
       </c>
       <c r="Q4" t="n">
-        <v>1251949000</v>
+        <v>1972393000</v>
       </c>
       <c r="R4" t="n">
-        <v>794000</v>
+        <v>1999000</v>
       </c>
       <c r="S4" t="n">
-        <v>-224056000</v>
+        <v>-116111000</v>
       </c>
       <c r="T4" t="n">
-        <v>1528231808</v>
+        <v>1791339452</v>
       </c>
       <c r="U4" t="n">
-        <v>1528231808</v>
+        <v>1791339452</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.28</v>
+        <v>-0.19</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.28</v>
+        <v>-0.19</v>
       </c>
       <c r="X4" t="n">
-        <v>-420736000</v>
+        <v>-347172000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-420736000</v>
+        <v>-347172000</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-420736000</v>
+        <v>-347172000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-1160000</v>
+        <v>18817000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-419576000</v>
-      </c>
-      <c r="AD4" t="n">
+        <v>-365989000</v>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="n">
+        <v>-365989000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-239000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-366228000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>25342000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>8070000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-8070000</v>
+      </c>
+      <c r="AK4" t="n">
         <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-419576000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-333000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-419909000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>19991000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-27526000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>14664000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>12862000</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>-184598000</v>
+        <v>-149154000</v>
       </c>
       <c r="AO4" t="n">
-        <v>198278000</v>
+        <v>161070000</v>
       </c>
       <c r="AP4" t="n">
-        <v>13680000</v>
+        <v>11916000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-52037000</v>
+        <v>-138673000</v>
       </c>
       <c r="AR4" t="n">
-        <v>254147000</v>
+        <v>539798000</v>
       </c>
       <c r="AS4" t="n">
-        <v>16192000</v>
+        <v>247476000</v>
       </c>
       <c r="AT4" t="n">
-        <v>64509000</v>
+        <v>104344000</v>
       </c>
       <c r="AU4" t="n">
-        <v>192119000</v>
+        <v>216816000</v>
       </c>
       <c r="AV4" t="n">
-        <v>55348000</v>
+        <v>62009000</v>
       </c>
       <c r="AW4" t="n">
-        <v>136771000</v>
+        <v>154807000</v>
       </c>
       <c r="AX4" t="n">
-        <v>202110000</v>
+        <v>401125000</v>
       </c>
       <c r="AY4" t="n">
-        <v>997802000</v>
+        <v>1432595000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1199912000</v>
+        <v>1833720000</v>
       </c>
       <c r="BA4" t="n">
-        <v>1199912000</v>
+        <v>1833720000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-1242139.076691</v>
+        <v>-1163318.233972</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001928</v>
+        <v>0.029982</v>
       </c>
       <c r="D5" t="n">
-        <v>-244470000</v>
+        <v>-139675000</v>
       </c>
       <c r="E5" t="n">
-        <v>-369059000</v>
+        <v>-38800000</v>
       </c>
       <c r="F5" t="n">
-        <v>-644162000</v>
+        <v>-38800000</v>
       </c>
       <c r="G5" t="n">
-        <v>-751317000</v>
+        <v>-393183000</v>
       </c>
       <c r="H5" t="n">
-        <v>76335000</v>
+        <v>72913000</v>
       </c>
       <c r="I5" t="n">
-        <v>923539000</v>
+        <v>1844587000</v>
       </c>
       <c r="J5" t="n">
-        <v>-613529000</v>
+        <v>-178475000</v>
       </c>
       <c r="K5" t="n">
-        <v>-689864000</v>
+        <v>-251388000</v>
       </c>
       <c r="L5" t="n">
-        <v>-176439000</v>
+        <v>-230823000</v>
       </c>
       <c r="M5" t="n">
-        <v>197445000</v>
+        <v>234063000</v>
       </c>
       <c r="N5" t="n">
-        <v>21006000</v>
+        <v>3240000</v>
       </c>
       <c r="O5" t="n">
-        <v>166705860.923309</v>
+        <v>-355546318.233972</v>
       </c>
       <c r="P5" t="n">
-        <v>-968233000</v>
+        <v>-393183000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1217407000</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>2404952000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>3313000</v>
+      </c>
       <c r="S5" t="n">
-        <v>-502642000</v>
+        <v>-218980000</v>
       </c>
       <c r="T5" t="n">
-        <v>1097308462</v>
+        <v>1848000000</v>
       </c>
       <c r="U5" t="n">
-        <v>1097308462</v>
+        <v>1848000000</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-0.88</v>
-      </c>
+        <v>-0.21</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>-968233000</v>
+        <v>-393183000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-968233000</v>
+        <v>-393183000</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-968233000</v>
+        <v>-393183000</v>
       </c>
       <c r="AB5" t="n">
-        <v>134281000</v>
+        <v>77713000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1102514000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>-216916000</v>
-      </c>
+        <v>-470896000</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>-885598000</v>
+        <v>-470896000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-1711000</v>
+        <v>-14555000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-887309000</v>
+        <v>-485451000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-16203000</v>
+        <v>46963000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-471676000</v>
+        <v>-4616000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-10694000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>103267000</v>
-      </c>
+        <v>-3672000</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>104000000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
+        <v>8288000</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>-176439000</v>
+        <v>-230823000</v>
       </c>
       <c r="AO5" t="n">
-        <v>197445000</v>
+        <v>234063000</v>
       </c>
       <c r="AP5" t="n">
-        <v>21006000</v>
+        <v>3240000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-123577000</v>
+        <v>-217736000</v>
       </c>
       <c r="AR5" t="n">
-        <v>293868000</v>
+        <v>560365000</v>
       </c>
       <c r="AS5" t="n">
-        <v>18919000</v>
+        <v>182516000</v>
       </c>
       <c r="AT5" t="n">
-        <v>59903000</v>
+        <v>115723000</v>
       </c>
       <c r="AU5" t="n">
-        <v>252722000</v>
+        <v>290340000</v>
       </c>
       <c r="AV5" t="n">
-        <v>114636000</v>
+        <v>82375000</v>
       </c>
       <c r="AW5" t="n">
-        <v>138086000</v>
+        <v>207965000</v>
       </c>
       <c r="AX5" t="n">
-        <v>170291000</v>
+        <v>342629000</v>
       </c>
       <c r="AY5" t="n">
-        <v>923539000</v>
+        <v>1844587000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1093830000</v>
+        <v>2187216000</v>
       </c>
       <c r="BA5" t="n">
-        <v>1093830000</v>
+        <v>2187216000</v>
       </c>
     </row>
   </sheetData>
@@ -1686,844 +1686,844 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>1848000000</v>
+        <v>1345200000</v>
       </c>
       <c r="C2" t="n">
-        <v>1848000000</v>
+        <v>1345200000</v>
       </c>
       <c r="D2" t="n">
-        <v>2984304000</v>
+        <v>2155598000</v>
       </c>
       <c r="E2" t="n">
-        <v>3141899000</v>
+        <v>2389771000</v>
       </c>
       <c r="F2" t="n">
-        <v>-1986695000</v>
+        <v>-1010078000</v>
       </c>
       <c r="G2" t="n">
-        <v>1254332000</v>
+        <v>1517218000</v>
       </c>
       <c r="H2" t="n">
-        <v>-2478933000</v>
+        <v>-1238837000</v>
       </c>
       <c r="I2" t="n">
-        <v>-1986695000</v>
+        <v>-1010078000</v>
       </c>
       <c r="J2" t="n">
-        <v>10211000</v>
+        <v>13809000</v>
       </c>
       <c r="K2" t="n">
-        <v>-1877356000</v>
+        <v>-858744000</v>
       </c>
       <c r="L2" t="n">
-        <v>-1695524000</v>
+        <v>-385133000</v>
       </c>
       <c r="M2" t="n">
-        <v>-1903504000</v>
+        <v>-788165000</v>
       </c>
       <c r="N2" t="n">
-        <v>-26148000</v>
+        <v>70579000</v>
       </c>
       <c r="O2" t="n">
-        <v>-1877356000</v>
+        <v>-858744000</v>
       </c>
       <c r="P2" t="n">
         <v>4360000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2010161000</v>
+        <v>-944428000</v>
       </c>
       <c r="R2" t="n">
+        <v>31495000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>112290000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>112290000</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3844379000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>563322000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>137000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>48534000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>38172000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>476479000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2868000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>473611000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3281057000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1913292000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>10941000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1902351000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>49507000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>865395000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-137000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>54412000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>811120000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>3056214000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1013994000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>228238000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>224080000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>4158000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>151334000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>151334000</v>
+      </c>
+      <c r="AT2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="n">
-        <v>155959000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>155959000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>4991242000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>237097000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="n">
-        <v>23638000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>27375000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>186084000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>4252000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>181832000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>4754145000</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="n">
-        <v>2955815000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>5959000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2949856000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>52038000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1401487000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>52188000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>26553000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1322746000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>3087738000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>812526000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>87827000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>71139000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>16688000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>109339000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>109339000</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="n">
-        <v>615360000</v>
+        <v>616659000</v>
       </c>
       <c r="AV2" t="n">
-        <v>-520717000</v>
+        <v>-380908000</v>
       </c>
       <c r="AW2" t="n">
-        <v>1136077000</v>
+        <v>997567000</v>
       </c>
       <c r="AX2" t="n">
-        <v>63843000</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+        <v>48929000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>616659000</v>
+      </c>
       <c r="AZ2" t="n">
-        <v>657180000</v>
+        <v>553120000</v>
       </c>
       <c r="BA2" t="n">
-        <v>327842000</v>
+        <v>276328000</v>
       </c>
       <c r="BB2" t="n">
-        <v>87212000</v>
+        <v>119190000</v>
       </c>
       <c r="BC2" t="n">
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>2275212000</v>
+        <v>2042220000</v>
       </c>
       <c r="BE2" t="n">
-        <v>228662000</v>
+        <v>192064000</v>
       </c>
       <c r="BF2" t="n">
-        <v>113076000</v>
+        <v>7732000</v>
       </c>
       <c r="BG2" t="n">
-        <v>141824000</v>
+        <v>76105000</v>
       </c>
       <c r="BH2" t="n">
-        <v>111614000</v>
+        <v>51236000</v>
       </c>
       <c r="BI2" t="n">
-        <v>1338000</v>
+        <v>10116000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>28872000</v>
+        <v>14753000</v>
       </c>
       <c r="BK2" t="n">
-        <v>501918000</v>
-      </c>
-      <c r="BL2" t="inlineStr"/>
+        <v>303517000</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0</v>
+      </c>
       <c r="BM2" t="n">
-        <v>969054000</v>
+        <v>851164000</v>
       </c>
       <c r="BN2" t="n">
-        <v>-278500000</v>
+        <v>-40252000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1247554000</v>
+        <v>437880000</v>
       </c>
       <c r="BP2" t="n">
-        <v>320678000</v>
+        <v>619370000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>173294000</v>
+        <v>399006000</v>
       </c>
       <c r="BR2" t="n">
-        <v>147384000</v>
-      </c>
-      <c r="BS2" t="inlineStr"/>
+        <v>220364000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>7732000</v>
+      </c>
       <c r="BT2" t="n">
-        <v>147384000</v>
+        <v>220364000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>1848000000</v>
+        <v>1722660000</v>
       </c>
       <c r="C3" t="n">
-        <v>1848000000</v>
+        <v>1722660000</v>
       </c>
       <c r="D3" t="n">
-        <v>2476140000</v>
+        <v>2120251000</v>
       </c>
       <c r="E3" t="n">
-        <v>2666736000</v>
+        <v>2289547000</v>
       </c>
       <c r="F3" t="n">
-        <v>-1608354000</v>
+        <v>-1240545000</v>
       </c>
       <c r="G3" t="n">
-        <v>1178448000</v>
+        <v>1184344000</v>
       </c>
       <c r="H3" t="n">
-        <v>-1809672000</v>
+        <v>-1291510000</v>
       </c>
       <c r="I3" t="n">
-        <v>-1608354000</v>
+        <v>-1240545000</v>
       </c>
       <c r="J3" t="n">
-        <v>18983000</v>
+        <v>7940000</v>
       </c>
       <c r="K3" t="n">
-        <v>-1469305000</v>
+        <v>-1097263000</v>
       </c>
       <c r="L3" t="n">
-        <v>-1087745000</v>
+        <v>-530704000</v>
       </c>
       <c r="M3" t="n">
-        <v>-1417815000</v>
+        <v>-1026852000</v>
       </c>
       <c r="N3" t="n">
-        <v>51490000</v>
+        <v>70411000</v>
       </c>
       <c r="O3" t="n">
-        <v>-1469305000</v>
+        <v>-1097263000</v>
       </c>
       <c r="P3" t="n">
         <v>4360000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1616978000</v>
+        <v>-1365164000</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>100795000</v>
       </c>
       <c r="S3" t="n">
-        <v>155959000</v>
+        <v>144631000</v>
       </c>
       <c r="T3" t="n">
-        <v>155959000</v>
+        <v>144631000</v>
       </c>
       <c r="U3" t="n">
-        <v>4225123000</v>
+        <v>3778050000</v>
       </c>
       <c r="V3" t="n">
-        <v>454778000</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
+        <v>640174000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>137000</v>
+      </c>
       <c r="X3" t="n">
-        <v>30386000</v>
+        <v>35157000</v>
       </c>
       <c r="Y3" t="n">
-        <v>34668000</v>
+        <v>36420000</v>
       </c>
       <c r="Z3" t="n">
-        <v>389724000</v>
+        <v>568460000</v>
       </c>
       <c r="AA3" t="n">
-        <v>8164000</v>
+        <v>1901000</v>
       </c>
       <c r="AB3" t="n">
-        <v>381560000</v>
+        <v>566559000</v>
       </c>
       <c r="AC3" t="n">
-        <v>3770345000</v>
+        <v>3137876000</v>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>2277012000</v>
+        <v>1721087000</v>
       </c>
       <c r="AF3" t="n">
-        <v>10819000</v>
+        <v>6039000</v>
       </c>
       <c r="AG3" t="n">
-        <v>2266193000</v>
+        <v>1715048000</v>
       </c>
       <c r="AH3" t="n">
-        <v>58359000</v>
+        <v>56085000</v>
       </c>
       <c r="AI3" t="n">
-        <v>1107272000</v>
+        <v>1193542000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>57196000</v>
+        <v>60237000</v>
       </c>
       <c r="AK3" t="n">
-        <v>38056000</v>
+        <v>71371000</v>
       </c>
       <c r="AL3" t="n">
-        <v>1012020000</v>
+        <v>1061934000</v>
       </c>
       <c r="AM3" t="n">
-        <v>2807308000</v>
+        <v>2751198000</v>
       </c>
       <c r="AN3" t="n">
-        <v>846635000</v>
+        <v>904832000</v>
       </c>
       <c r="AO3" t="n">
-        <v>88871000</v>
+        <v>144971000</v>
       </c>
       <c r="AP3" t="n">
-        <v>65727000</v>
+        <v>140444000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>23144000</v>
+        <v>4527000</v>
       </c>
       <c r="AR3" t="n">
-        <v>139049000</v>
+        <v>143282000</v>
       </c>
       <c r="AS3" t="n">
-        <v>139049000</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
+        <v>143282000</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
       <c r="AU3" t="n">
-        <v>610282000</v>
+        <v>608085000</v>
       </c>
       <c r="AV3" t="n">
-        <v>-470680000</v>
+        <v>-425811000</v>
       </c>
       <c r="AW3" t="n">
-        <v>1080962000</v>
+        <v>1033896000</v>
       </c>
       <c r="AX3" t="n">
-        <v>32159000</v>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+        <v>49237000</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>608085000</v>
+      </c>
       <c r="AZ3" t="n">
-        <v>607557000</v>
+        <v>584452000</v>
       </c>
       <c r="BA3" t="n">
-        <v>328627000</v>
+        <v>284497000</v>
       </c>
       <c r="BB3" t="n">
-        <v>112619000</v>
+        <v>115710000</v>
       </c>
       <c r="BC3" t="n">
         <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>1960673000</v>
+        <v>1846366000</v>
       </c>
       <c r="BE3" t="n">
-        <v>245134000</v>
+        <v>248675000</v>
       </c>
       <c r="BF3" t="n">
-        <v>51270000</v>
+        <v>35725000</v>
       </c>
       <c r="BG3" t="n">
-        <v>146302000</v>
+        <v>147129000</v>
       </c>
       <c r="BH3" t="n">
-        <v>95058000</v>
+        <v>119116000</v>
       </c>
       <c r="BI3" t="n">
-        <v>10935000</v>
+        <v>6303000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>40309000</v>
+        <v>21710000</v>
       </c>
       <c r="BK3" t="n">
-        <v>411286000</v>
+        <v>512070000</v>
       </c>
       <c r="BL3" t="inlineStr"/>
       <c r="BM3" t="n">
-        <v>693225000</v>
+        <v>447524000</v>
       </c>
       <c r="BN3" t="n">
-        <v>-173625000</v>
+        <v>-38044000</v>
       </c>
       <c r="BO3" t="n">
-        <v>866850000</v>
+        <v>485568000</v>
       </c>
       <c r="BP3" t="n">
-        <v>413456000</v>
+        <v>455243000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>241843000</v>
+        <v>293887000</v>
       </c>
       <c r="BR3" t="n">
-        <v>171613000</v>
+        <v>161356000</v>
       </c>
       <c r="BS3" t="inlineStr"/>
       <c r="BT3" t="n">
-        <v>171613000</v>
+        <v>161356000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>1722660000</v>
+        <v>1848000000</v>
       </c>
       <c r="C4" t="n">
-        <v>1722660000</v>
+        <v>1848000000</v>
       </c>
       <c r="D4" t="n">
-        <v>2120251000</v>
+        <v>2476140000</v>
       </c>
       <c r="E4" t="n">
-        <v>2289547000</v>
+        <v>2666736000</v>
       </c>
       <c r="F4" t="n">
-        <v>-1240545000</v>
+        <v>-1608354000</v>
       </c>
       <c r="G4" t="n">
-        <v>1184344000</v>
+        <v>1178448000</v>
       </c>
       <c r="H4" t="n">
-        <v>-1291510000</v>
+        <v>-1809672000</v>
       </c>
       <c r="I4" t="n">
-        <v>-1240545000</v>
+        <v>-1608354000</v>
       </c>
       <c r="J4" t="n">
-        <v>7940000</v>
+        <v>18983000</v>
       </c>
       <c r="K4" t="n">
-        <v>-1097263000</v>
+        <v>-1469305000</v>
       </c>
       <c r="L4" t="n">
-        <v>-530704000</v>
+        <v>-1087745000</v>
       </c>
       <c r="M4" t="n">
-        <v>-1026852000</v>
+        <v>-1417815000</v>
       </c>
       <c r="N4" t="n">
-        <v>70411000</v>
+        <v>51490000</v>
       </c>
       <c r="O4" t="n">
-        <v>-1097263000</v>
+        <v>-1469305000</v>
       </c>
       <c r="P4" t="n">
         <v>4360000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1365164000</v>
+        <v>-1616978000</v>
       </c>
       <c r="R4" t="n">
-        <v>100795000</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>144631000</v>
+        <v>155959000</v>
       </c>
       <c r="T4" t="n">
-        <v>144631000</v>
+        <v>155959000</v>
       </c>
       <c r="U4" t="n">
-        <v>3778050000</v>
+        <v>4225123000</v>
       </c>
       <c r="V4" t="n">
-        <v>640174000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>137000</v>
-      </c>
+        <v>454778000</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>35157000</v>
+        <v>30386000</v>
       </c>
       <c r="Y4" t="n">
-        <v>36420000</v>
+        <v>34668000</v>
       </c>
       <c r="Z4" t="n">
-        <v>568460000</v>
+        <v>389724000</v>
       </c>
       <c r="AA4" t="n">
-        <v>1901000</v>
+        <v>8164000</v>
       </c>
       <c r="AB4" t="n">
-        <v>566559000</v>
+        <v>381560000</v>
       </c>
       <c r="AC4" t="n">
-        <v>3137876000</v>
+        <v>3770345000</v>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>1721087000</v>
+        <v>2277012000</v>
       </c>
       <c r="AF4" t="n">
-        <v>6039000</v>
+        <v>10819000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1715048000</v>
+        <v>2266193000</v>
       </c>
       <c r="AH4" t="n">
-        <v>56085000</v>
+        <v>58359000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1193542000</v>
+        <v>1107272000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>60237000</v>
+        <v>57196000</v>
       </c>
       <c r="AK4" t="n">
-        <v>71371000</v>
+        <v>38056000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1061934000</v>
+        <v>1012020000</v>
       </c>
       <c r="AM4" t="n">
-        <v>2751198000</v>
+        <v>2807308000</v>
       </c>
       <c r="AN4" t="n">
-        <v>904832000</v>
+        <v>846635000</v>
       </c>
       <c r="AO4" t="n">
-        <v>144971000</v>
+        <v>88871000</v>
       </c>
       <c r="AP4" t="n">
-        <v>140444000</v>
+        <v>65727000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4527000</v>
+        <v>23144000</v>
       </c>
       <c r="AR4" t="n">
-        <v>143282000</v>
+        <v>139049000</v>
       </c>
       <c r="AS4" t="n">
-        <v>143282000</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
+        <v>139049000</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="n">
-        <v>608085000</v>
+        <v>610282000</v>
       </c>
       <c r="AV4" t="n">
-        <v>-425811000</v>
+        <v>-470680000</v>
       </c>
       <c r="AW4" t="n">
-        <v>1033896000</v>
+        <v>1080962000</v>
       </c>
       <c r="AX4" t="n">
-        <v>49237000</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>608085000</v>
-      </c>
+        <v>32159000</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="n">
-        <v>584452000</v>
+        <v>607557000</v>
       </c>
       <c r="BA4" t="n">
-        <v>284497000</v>
+        <v>328627000</v>
       </c>
       <c r="BB4" t="n">
-        <v>115710000</v>
+        <v>112619000</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>1846366000</v>
+        <v>1960673000</v>
       </c>
       <c r="BE4" t="n">
-        <v>248675000</v>
+        <v>245134000</v>
       </c>
       <c r="BF4" t="n">
-        <v>35725000</v>
+        <v>51270000</v>
       </c>
       <c r="BG4" t="n">
-        <v>147129000</v>
+        <v>146302000</v>
       </c>
       <c r="BH4" t="n">
-        <v>119116000</v>
+        <v>95058000</v>
       </c>
       <c r="BI4" t="n">
-        <v>6303000</v>
+        <v>10935000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>21710000</v>
+        <v>40309000</v>
       </c>
       <c r="BK4" t="n">
-        <v>512070000</v>
+        <v>411286000</v>
       </c>
       <c r="BL4" t="inlineStr"/>
       <c r="BM4" t="n">
-        <v>447524000</v>
+        <v>693225000</v>
       </c>
       <c r="BN4" t="n">
-        <v>-38044000</v>
+        <v>-173625000</v>
       </c>
       <c r="BO4" t="n">
-        <v>485568000</v>
+        <v>866850000</v>
       </c>
       <c r="BP4" t="n">
-        <v>455243000</v>
+        <v>413456000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>293887000</v>
+        <v>241843000</v>
       </c>
       <c r="BR4" t="n">
-        <v>161356000</v>
+        <v>171613000</v>
       </c>
       <c r="BS4" t="inlineStr"/>
       <c r="BT4" t="n">
-        <v>161356000</v>
+        <v>171613000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>1345200000</v>
+        <v>1848000000</v>
       </c>
       <c r="C5" t="n">
-        <v>1345200000</v>
+        <v>1848000000</v>
       </c>
       <c r="D5" t="n">
-        <v>2155598000</v>
+        <v>2984304000</v>
       </c>
       <c r="E5" t="n">
-        <v>2389771000</v>
+        <v>3141899000</v>
       </c>
       <c r="F5" t="n">
-        <v>-1010078000</v>
+        <v>-1986695000</v>
       </c>
       <c r="G5" t="n">
-        <v>1517218000</v>
+        <v>1254332000</v>
       </c>
       <c r="H5" t="n">
-        <v>-1238837000</v>
+        <v>-2478933000</v>
       </c>
       <c r="I5" t="n">
-        <v>-1010078000</v>
+        <v>-1986695000</v>
       </c>
       <c r="J5" t="n">
-        <v>13809000</v>
+        <v>10211000</v>
       </c>
       <c r="K5" t="n">
-        <v>-858744000</v>
+        <v>-1877356000</v>
       </c>
       <c r="L5" t="n">
-        <v>-385133000</v>
+        <v>-1695524000</v>
       </c>
       <c r="M5" t="n">
-        <v>-788165000</v>
+        <v>-1903504000</v>
       </c>
       <c r="N5" t="n">
-        <v>70579000</v>
+        <v>-26148000</v>
       </c>
       <c r="O5" t="n">
-        <v>-858744000</v>
+        <v>-1877356000</v>
       </c>
       <c r="P5" t="n">
         <v>4360000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-944428000</v>
+        <v>-2010161000</v>
       </c>
       <c r="R5" t="n">
-        <v>31495000</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>112290000</v>
+        <v>155959000</v>
       </c>
       <c r="T5" t="n">
-        <v>112290000</v>
+        <v>155959000</v>
       </c>
       <c r="U5" t="n">
-        <v>3844379000</v>
+        <v>4991242000</v>
       </c>
       <c r="V5" t="n">
-        <v>563322000</v>
-      </c>
-      <c r="W5" t="n">
-        <v>137000</v>
-      </c>
+        <v>237097000</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>48534000</v>
+        <v>23638000</v>
       </c>
       <c r="Y5" t="n">
-        <v>38172000</v>
+        <v>27375000</v>
       </c>
       <c r="Z5" t="n">
-        <v>476479000</v>
+        <v>186084000</v>
       </c>
       <c r="AA5" t="n">
-        <v>2868000</v>
+        <v>4252000</v>
       </c>
       <c r="AB5" t="n">
-        <v>473611000</v>
+        <v>181832000</v>
       </c>
       <c r="AC5" t="n">
-        <v>3281057000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>4000</v>
-      </c>
+        <v>4754145000</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>1913292000</v>
+        <v>2955815000</v>
       </c>
       <c r="AF5" t="n">
-        <v>10941000</v>
+        <v>5959000</v>
       </c>
       <c r="AG5" t="n">
-        <v>1902351000</v>
+        <v>2949856000</v>
       </c>
       <c r="AH5" t="n">
-        <v>49507000</v>
+        <v>52038000</v>
       </c>
       <c r="AI5" t="n">
-        <v>865395000</v>
+        <v>1401487000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-137000</v>
+        <v>52188000</v>
       </c>
       <c r="AK5" t="n">
-        <v>54412000</v>
+        <v>26553000</v>
       </c>
       <c r="AL5" t="n">
-        <v>811120000</v>
+        <v>1322746000</v>
       </c>
       <c r="AM5" t="n">
-        <v>3056214000</v>
+        <v>3087738000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1013994000</v>
+        <v>812526000</v>
       </c>
       <c r="AO5" t="n">
-        <v>228238000</v>
+        <v>87827000</v>
       </c>
       <c r="AP5" t="n">
-        <v>224080000</v>
+        <v>71139000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4158000</v>
+        <v>16688000</v>
       </c>
       <c r="AR5" t="n">
-        <v>151334000</v>
+        <v>109339000</v>
       </c>
       <c r="AS5" t="n">
-        <v>151334000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
+        <v>109339000</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="n">
-        <v>616659000</v>
+        <v>615360000</v>
       </c>
       <c r="AV5" t="n">
-        <v>-380908000</v>
+        <v>-520717000</v>
       </c>
       <c r="AW5" t="n">
-        <v>997567000</v>
+        <v>1136077000</v>
       </c>
       <c r="AX5" t="n">
-        <v>48929000</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>616659000</v>
-      </c>
+        <v>63843000</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="n">
-        <v>553120000</v>
+        <v>657180000</v>
       </c>
       <c r="BA5" t="n">
-        <v>276328000</v>
+        <v>327842000</v>
       </c>
       <c r="BB5" t="n">
-        <v>119190000</v>
+        <v>87212000</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>2042220000</v>
+        <v>2275212000</v>
       </c>
       <c r="BE5" t="n">
-        <v>192064000</v>
+        <v>228662000</v>
       </c>
       <c r="BF5" t="n">
-        <v>7732000</v>
+        <v>113076000</v>
       </c>
       <c r="BG5" t="n">
-        <v>76105000</v>
+        <v>141824000</v>
       </c>
       <c r="BH5" t="n">
-        <v>51236000</v>
+        <v>111614000</v>
       </c>
       <c r="BI5" t="n">
-        <v>10116000</v>
+        <v>1338000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>14753000</v>
+        <v>28872000</v>
       </c>
       <c r="BK5" t="n">
-        <v>303517000</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>0</v>
-      </c>
+        <v>501918000</v>
+      </c>
+      <c r="BL5" t="inlineStr"/>
       <c r="BM5" t="n">
-        <v>851164000</v>
+        <v>969054000</v>
       </c>
       <c r="BN5" t="n">
-        <v>-40252000</v>
+        <v>-278500000</v>
       </c>
       <c r="BO5" t="n">
-        <v>437880000</v>
+        <v>1247554000</v>
       </c>
       <c r="BP5" t="n">
-        <v>619370000</v>
+        <v>320678000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>399006000</v>
+        <v>173294000</v>
       </c>
       <c r="BR5" t="n">
-        <v>220364000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>7732000</v>
-      </c>
+        <v>147384000</v>
+      </c>
+      <c r="BS5" t="inlineStr"/>
       <c r="BT5" t="n">
-        <v>220364000</v>
+        <v>147384000</v>
       </c>
     </row>
   </sheetData>
@@ -2804,614 +2804,614 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-282471000</v>
+        <v>-73701000</v>
       </c>
       <c r="C2" t="n">
-        <v>-613951000</v>
+        <v>-693118000</v>
       </c>
       <c r="D2" t="n">
-        <v>837531000</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>700748000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>51433000</v>
+      </c>
       <c r="F2" t="n">
-        <v>-102903000</v>
+        <v>-16283000</v>
       </c>
       <c r="G2" t="n">
-        <v>147384000</v>
+        <v>228096000</v>
       </c>
       <c r="H2" t="n">
-        <v>171613000</v>
+        <v>226059000</v>
       </c>
       <c r="I2" t="n">
-        <v>-862000</v>
+        <v>-925000</v>
       </c>
       <c r="J2" t="n">
-        <v>-23367000</v>
+        <v>2962000</v>
       </c>
       <c r="K2" t="n">
-        <v>193723000</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
+        <v>-80569000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-10503000</v>
+      </c>
       <c r="M2" t="n">
-        <v>-20468000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+        <v>-101542000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>51433000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>51433000</v>
+      </c>
       <c r="P2" t="n">
-        <v>223580000</v>
+        <v>7630000</v>
       </c>
       <c r="Q2" t="n">
-        <v>223580000</v>
+        <v>7630000</v>
       </c>
       <c r="R2" t="n">
-        <v>-613951000</v>
+        <v>-693118000</v>
       </c>
       <c r="S2" t="n">
-        <v>837531000</v>
+        <v>700748000</v>
       </c>
       <c r="T2" t="n">
-        <v>-37522000</v>
+        <v>140949000</v>
       </c>
       <c r="U2" t="n">
-        <v>664000</v>
+        <v>85398000</v>
       </c>
       <c r="V2" t="n">
-        <v>3240000</v>
+        <v>21006000</v>
       </c>
       <c r="W2" t="n">
-        <v>6000</v>
+        <v>5632000</v>
       </c>
       <c r="X2" t="n">
-        <v>9918000</v>
+        <v>43514000</v>
       </c>
       <c r="Y2" t="n">
-        <v>19235000</v>
+        <v>73961000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-9317000</v>
+        <v>-30447000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-6422000</v>
+        <v>1682000</v>
       </c>
       <c r="AB2" t="n">
+        <v>1682000</v>
+      </c>
+      <c r="AC2" t="n">
         <v>0</v>
       </c>
-      <c r="AC2" t="n">
-        <v>-6422000</v>
-      </c>
       <c r="AD2" t="n">
-        <v>-4395000</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-4395000</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>-77733000</v>
+        <v>-16283000</v>
       </c>
       <c r="AG2" t="n">
-        <v>20775000</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-98508000</v>
+        <v>-16283000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-179568000</v>
+        <v>-57418000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-355000</v>
+        <v>8179000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-328316000</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
+        <v>123973000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>85071000</v>
+      </c>
       <c r="AM2" t="n">
-        <v>9845000</v>
+        <v>-289777000</v>
       </c>
       <c r="AN2" t="n">
-        <v>371953000</v>
+        <v>265349000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-28305000</v>
+        <v>25596000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-651814000</v>
+        <v>149119000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>224031000</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
+        <v>175761000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
       <c r="AS2" t="n">
-        <v>238973000</v>
+        <v>64710000</v>
       </c>
       <c r="AT2" t="n">
-        <v>72913000</v>
+        <v>76335000</v>
       </c>
       <c r="AU2" t="n">
-        <v>10547000</v>
+        <v>11921000</v>
       </c>
       <c r="AV2" t="n">
-        <v>62366000</v>
+        <v>64414000</v>
       </c>
       <c r="AW2" t="n">
-        <v>34178000</v>
+        <v>166854000</v>
       </c>
       <c r="AX2" t="n">
-        <v>39456000</v>
+        <v>-139572000</v>
       </c>
       <c r="AY2" t="n">
-        <v>1673000</v>
+        <v>4479000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-5345000</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>-485451000</v>
+        <v>-887309000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-170195000</v>
+        <v>5572000</v>
       </c>
       <c r="C3" t="n">
-        <v>-329204000</v>
+        <v>-765166000</v>
       </c>
       <c r="D3" t="n">
-        <v>552226000</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>595246000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
       <c r="F3" t="n">
-        <v>-40661000</v>
+        <v>-49965000</v>
       </c>
       <c r="G3" t="n">
-        <v>171613000</v>
+        <v>161365000</v>
       </c>
       <c r="H3" t="n">
-        <v>161365000</v>
+        <v>228096000</v>
       </c>
       <c r="I3" t="n">
-        <v>921000</v>
+        <v>3229000</v>
       </c>
       <c r="J3" t="n">
-        <v>9327000</v>
+        <v>-69960000</v>
       </c>
       <c r="K3" t="n">
-        <v>185004000</v>
+        <v>-224715000</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>-30046000</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+        <v>-44692000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
       <c r="P3" t="n">
-        <v>223022000</v>
+        <v>-169920000</v>
       </c>
       <c r="Q3" t="n">
-        <v>223022000</v>
+        <v>-169920000</v>
       </c>
       <c r="R3" t="n">
-        <v>-329204000</v>
+        <v>-765166000</v>
       </c>
       <c r="S3" t="n">
-        <v>552226000</v>
+        <v>595246000</v>
       </c>
       <c r="T3" t="n">
-        <v>-46143000</v>
+        <v>99218000</v>
       </c>
       <c r="U3" t="n">
-        <v>4354000</v>
+        <v>54450000</v>
       </c>
       <c r="V3" t="n">
-        <v>5065000</v>
+        <v>13680000</v>
       </c>
       <c r="W3" t="n">
-        <v>1820000</v>
+        <v>3035000</v>
       </c>
       <c r="X3" t="n">
-        <v>19602000</v>
+        <v>74577000</v>
       </c>
       <c r="Y3" t="n">
-        <v>130568000</v>
+        <v>94278000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-110966000</v>
+        <v>-19701000</v>
       </c>
       <c r="AA3" t="n">
-        <v>270000</v>
+        <v>3441000</v>
       </c>
       <c r="AB3" t="n">
-        <v>270000</v>
-      </c>
-      <c r="AC3" t="n">
+        <v>3441000</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="n">
+        <v>-369000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>-369000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-49596000</v>
+      </c>
+      <c r="AG3" t="n">
         <v>0</v>
       </c>
-      <c r="AD3" t="n">
-        <v>-2822000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>-2822000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-37232000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>607000</v>
-      </c>
       <c r="AH3" t="n">
-        <v>-37839000</v>
+        <v>-49596000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-129534000</v>
+        <v>55537000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-30095000</v>
+        <v>5919000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-280804000</v>
+        <v>-9775000</v>
       </c>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
-        <v>42771000</v>
+        <v>-65275000</v>
       </c>
       <c r="AN3" t="n">
-        <v>68105000</v>
+        <v>80796000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-4615000</v>
+        <v>-82178000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-368121000</v>
+        <v>83646000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>143652000</v>
+        <v>171078000</v>
       </c>
       <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>274136000</v>
+        <v>49534000</v>
       </c>
       <c r="AT3" t="n">
-        <v>64090000</v>
+        <v>69338000</v>
       </c>
       <c r="AU3" t="n">
-        <v>8982000</v>
+        <v>8380000</v>
       </c>
       <c r="AV3" t="n">
-        <v>55108000</v>
+        <v>60958000</v>
       </c>
       <c r="AW3" t="n">
-        <v>27003000</v>
+        <v>-41661000</v>
       </c>
       <c r="AX3" t="n">
-        <v>-13442000</v>
+        <v>168981000</v>
       </c>
       <c r="AY3" t="n">
-        <v>28000</v>
+        <v>1627000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-2661000</v>
+        <v>13050000</v>
       </c>
       <c r="BA3" t="n">
-        <v>-366228000</v>
+        <v>-419909000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>5572000</v>
+        <v>-170195000</v>
       </c>
       <c r="C4" t="n">
-        <v>-765166000</v>
+        <v>-329204000</v>
       </c>
       <c r="D4" t="n">
-        <v>595246000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
+        <v>552226000</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>-49965000</v>
+        <v>-40661000</v>
       </c>
       <c r="G4" t="n">
+        <v>171613000</v>
+      </c>
+      <c r="H4" t="n">
         <v>161365000</v>
       </c>
-      <c r="H4" t="n">
-        <v>228096000</v>
-      </c>
       <c r="I4" t="n">
-        <v>3229000</v>
+        <v>921000</v>
       </c>
       <c r="J4" t="n">
-        <v>-69960000</v>
+        <v>9327000</v>
       </c>
       <c r="K4" t="n">
-        <v>-224715000</v>
+        <v>185004000</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>-44692000</v>
-      </c>
-      <c r="N4" t="n">
+        <v>-30046000</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>223022000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>223022000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-329204000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>552226000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-46143000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4354000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>5065000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1820000</v>
+      </c>
+      <c r="X4" t="n">
+        <v>19602000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>130568000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-110966000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>270000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>270000</v>
+      </c>
+      <c r="AC4" t="n">
         <v>0</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>-169920000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-169920000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>-765166000</v>
-      </c>
-      <c r="S4" t="n">
-        <v>595246000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>99218000</v>
-      </c>
-      <c r="U4" t="n">
-        <v>54450000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>13680000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3035000</v>
-      </c>
-      <c r="X4" t="n">
-        <v>74577000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>94278000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-19701000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3441000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>3441000</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>-369000</v>
+        <v>-2822000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-369000</v>
+        <v>-2822000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-49596000</v>
+        <v>-37232000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>607000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-49596000</v>
+        <v>-37839000</v>
       </c>
       <c r="AI4" t="n">
-        <v>55537000</v>
+        <v>-129534000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>5919000</v>
+        <v>-30095000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-9775000</v>
+        <v>-280804000</v>
       </c>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
-        <v>-65275000</v>
+        <v>42771000</v>
       </c>
       <c r="AN4" t="n">
-        <v>80796000</v>
+        <v>68105000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-82178000</v>
+        <v>-4615000</v>
       </c>
       <c r="AP4" t="n">
-        <v>83646000</v>
+        <v>-368121000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>171078000</v>
+        <v>143652000</v>
       </c>
       <c r="AR4" t="inlineStr"/>
       <c r="AS4" t="n">
-        <v>49534000</v>
+        <v>274136000</v>
       </c>
       <c r="AT4" t="n">
-        <v>69338000</v>
+        <v>64090000</v>
       </c>
       <c r="AU4" t="n">
-        <v>8380000</v>
+        <v>8982000</v>
       </c>
       <c r="AV4" t="n">
-        <v>60958000</v>
+        <v>55108000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-41661000</v>
+        <v>27003000</v>
       </c>
       <c r="AX4" t="n">
-        <v>168981000</v>
+        <v>-13442000</v>
       </c>
       <c r="AY4" t="n">
-        <v>1627000</v>
+        <v>28000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13050000</v>
+        <v>-2661000</v>
       </c>
       <c r="BA4" t="n">
-        <v>-419909000</v>
+        <v>-366228000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-73701000</v>
+        <v>-282471000</v>
       </c>
       <c r="C5" t="n">
-        <v>-693118000</v>
+        <v>-613951000</v>
       </c>
       <c r="D5" t="n">
-        <v>700748000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>51433000</v>
-      </c>
+        <v>837531000</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>-16283000</v>
+        <v>-102903000</v>
       </c>
       <c r="G5" t="n">
-        <v>228096000</v>
+        <v>147384000</v>
       </c>
       <c r="H5" t="n">
-        <v>226059000</v>
+        <v>171613000</v>
       </c>
       <c r="I5" t="n">
-        <v>-925000</v>
+        <v>-862000</v>
       </c>
       <c r="J5" t="n">
-        <v>2962000</v>
+        <v>-23367000</v>
       </c>
       <c r="K5" t="n">
-        <v>-80569000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-10503000</v>
-      </c>
+        <v>193723000</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>-101542000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>51433000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>51433000</v>
-      </c>
+        <v>-20468000</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>7630000</v>
+        <v>223580000</v>
       </c>
       <c r="Q5" t="n">
-        <v>7630000</v>
+        <v>223580000</v>
       </c>
       <c r="R5" t="n">
-        <v>-693118000</v>
+        <v>-613951000</v>
       </c>
       <c r="S5" t="n">
-        <v>700748000</v>
+        <v>837531000</v>
       </c>
       <c r="T5" t="n">
-        <v>140949000</v>
+        <v>-37522000</v>
       </c>
       <c r="U5" t="n">
-        <v>85398000</v>
+        <v>664000</v>
       </c>
       <c r="V5" t="n">
-        <v>21006000</v>
+        <v>3240000</v>
       </c>
       <c r="W5" t="n">
-        <v>5632000</v>
+        <v>6000</v>
       </c>
       <c r="X5" t="n">
-        <v>43514000</v>
+        <v>9918000</v>
       </c>
       <c r="Y5" t="n">
-        <v>73961000</v>
+        <v>19235000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-30447000</v>
+        <v>-9317000</v>
       </c>
       <c r="AA5" t="n">
-        <v>1682000</v>
+        <v>-6422000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1682000</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>-6422000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>-4395000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>-4395000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-16283000</v>
+        <v>-77733000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>20775000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-16283000</v>
+        <v>-98508000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-57418000</v>
+        <v>-179568000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>8179000</v>
+        <v>-355000</v>
       </c>
       <c r="AK5" t="n">
-        <v>123973000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>85071000</v>
-      </c>
+        <v>-328316000</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
-        <v>-289777000</v>
+        <v>9845000</v>
       </c>
       <c r="AN5" t="n">
-        <v>265349000</v>
+        <v>371953000</v>
       </c>
       <c r="AO5" t="n">
-        <v>25596000</v>
+        <v>-28305000</v>
       </c>
       <c r="AP5" t="n">
-        <v>149119000</v>
+        <v>-651814000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>175761000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
+        <v>224031000</v>
+      </c>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>64710000</v>
+        <v>238973000</v>
       </c>
       <c r="AT5" t="n">
-        <v>76335000</v>
+        <v>72913000</v>
       </c>
       <c r="AU5" t="n">
-        <v>11921000</v>
+        <v>10547000</v>
       </c>
       <c r="AV5" t="n">
-        <v>64414000</v>
+        <v>62366000</v>
       </c>
       <c r="AW5" t="n">
-        <v>166854000</v>
+        <v>34178000</v>
       </c>
       <c r="AX5" t="n">
-        <v>-139572000</v>
+        <v>39456000</v>
       </c>
       <c r="AY5" t="n">
-        <v>4479000</v>
+        <v>1673000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-5345000</v>
       </c>
       <c r="BA5" t="n">
-        <v>-887309000</v>
+        <v>-485451000</v>
       </c>
     </row>
   </sheetData>
@@ -3911,29 +3911,29 @@
       </c>
       <c r="CS1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="CW1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
       <c r="CX1" t="inlineStr">
         <is>
           <t>exchange</t>
@@ -3971,132 +3971,132 @@
       </c>
       <c r="DE1" t="inlineStr">
         <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>priceToBook</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>priceToBook</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>marketState</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
         </is>
       </c>
       <c r="EE1" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Dr. Wilson  Sea', 'age': 61, 'title': 'Executive Chairman', 'yearBorn': 1964, 'fiscalYear': 2025, 'totalPay': 1467745, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Huanqiang  Zhu', 'age': 55, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1970, 'fiscalYear': 2025, 'totalPay': 110052, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Hui  Wang CPA', 'age': 46, 'title': 'CFO &amp; Executive President', 'yearBorn': 1979, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Bo  Sun', 'age': 51, 'title': 'Deputy Chief Executive Officer', 'yearBorn': 1974, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Chang  Liu', 'age': 43, 'title': 'Deputy Chief Executive Officer', 'yearBorn': 1982, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kwok Kee  Chan CPA', 'age': 52, 'title': 'Company Secretary', 'yearBorn': 1973, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Dr. Wilson  Sea', 'age': 61, 'title': 'Executive Chairman', 'yearBorn': 1964, 'fiscalYear': 2025, 'totalPay': 1466575, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Huanqiang  Zhu', 'age': 55, 'title': 'CEO &amp; Executive Director', 'yearBorn': 1970, 'fiscalYear': 2025, 'totalPay': 109964, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Bo  Sun', 'age': 51, 'title': 'Deputy Chief Executive Officer', 'yearBorn': 1974, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Chang  Liu', 'age': 43, 'title': 'Deputy Chief Executive Officer', 'yearBorn': 1982, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Kwok Kee  Chan CPA', 'age': 52, 'title': 'Company Secretary', 'yearBorn': 1973, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -4189,55 +4189,55 @@
         <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>0.038</v>
+        <v>0.037</v>
       </c>
       <c r="T2" t="n">
-        <v>0.038</v>
+        <v>0.037</v>
       </c>
       <c r="U2" t="n">
-        <v>0.035</v>
+        <v>0.034</v>
       </c>
       <c r="V2" t="n">
-        <v>0.038</v>
+        <v>0.037</v>
       </c>
       <c r="W2" t="n">
-        <v>0.038</v>
+        <v>0.037</v>
       </c>
       <c r="X2" t="n">
-        <v>0.038</v>
+        <v>0.037</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.035</v>
+        <v>0.034</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.038</v>
+        <v>0.037</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.038</v>
+        <v>0.017</v>
       </c>
       <c r="AC2" t="n">
-        <v>1050000</v>
+        <v>120000</v>
       </c>
       <c r="AD2" t="n">
-        <v>1050000</v>
+        <v>120000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1390680</v>
+        <v>1534915</v>
       </c>
       <c r="AF2" t="n">
-        <v>462400</v>
+        <v>1191280</v>
       </c>
       <c r="AG2" t="n">
-        <v>462400</v>
+        <v>1191280</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.035</v>
+        <v>0.034</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.038</v>
+        <v>0.037</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
@@ -4246,10 +4246,10 @@
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>70224000</v>
+        <v>68376000</v>
       </c>
       <c r="AM2" t="n">
-        <v>70224000</v>
+        <v>68376000</v>
       </c>
       <c r="AN2" t="n">
         <v>0.029</v>
@@ -4264,13 +4264,13 @@
         <v>0.025</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.02037378</v>
+        <v>0.019837629</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.03962</v>
+        <v>0.03762</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.050225</v>
+        <v>0.04915</v>
       </c>
       <c r="AU2" t="n">
         <v>0</v>
@@ -4287,7 +4287,7 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>3013011968</v>
+        <v>3011163904</v>
       </c>
       <c r="AZ2" t="n">
         <v>-0.09913000499999999</v>
@@ -4308,7 +4308,7 @@
         <v>1848000000</v>
       </c>
       <c r="BF2" t="n">
-        <v>-1.3330212</v>
+        <v>-1.3323138</v>
       </c>
       <c r="BG2" t="n">
         <v>1767139200</v>
@@ -4337,13 +4337,13 @@
         <v>0.874</v>
       </c>
       <c r="BO2" t="n">
-        <v>-1037.539</v>
+        <v>-1036.902</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>-0.21276593</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="BS2" t="n">
-        <v>0.038</v>
+        <v>0.037</v>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
@@ -4444,26 +4444,26 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CS2" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="CT2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CT2" t="n">
+        <v>1782113271</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="CV2" t="inlineStr">
         <is>
           <t>FIRST CAP GP</t>
         </is>
       </c>
-      <c r="CU2" t="inlineStr">
+      <c r="CW2" t="inlineStr">
         <is>
           <t>China First Capital Group Limited</t>
         </is>
-      </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="CW2" t="n">
-        <v>1780387724</v>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
@@ -4496,26 +4496,26 @@
       <c r="DD2" t="b">
         <v>0</v>
       </c>
-      <c r="DE2" t="b">
+      <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
         <v>-0.21</v>
       </c>
       <c r="DG2" t="n">
-        <v>-0.0016200021</v>
+        <v>-0.00062000006</v>
       </c>
       <c r="DH2" t="n">
-        <v>-0.040888492</v>
+        <v>-0.016480597</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.012225002</v>
+        <v>-0.012150001</v>
       </c>
       <c r="DJ2" t="n">
-        <v>-0.24340472</v>
+        <v>-0.24720246</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0.028506674</v>
+        <v>-0.027771236</v>
       </c>
       <c r="DL2" t="n">
         <v>15</v>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="DR2" t="inlineStr">
         <is>
-          <t>0.035 - 0.038</t>
+          <t>0.034 - 0.037</t>
         </is>
       </c>
       <c r="DS2" t="inlineStr">
@@ -4546,13 +4546,13 @@
         </is>
       </c>
       <c r="DT2" t="n">
-        <v>1390680</v>
+        <v>1534915</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008000001</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.31034482</v>
+        <v>0.27586213</v>
       </c>
       <c r="DW2" t="inlineStr">
         <is>
@@ -4560,13 +4560,13 @@
         </is>
       </c>
       <c r="DX2" t="n">
-        <v>-0.036000002</v>
+        <v>-0.037</v>
       </c>
       <c r="DY2" t="n">
-        <v>-0.48648652</v>
+        <v>-0.5</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0</v>
+        <v>-21.276592</v>
       </c>
       <c r="EA2" t="n">
         <v>1743026881</v>
@@ -4574,13 +4574,13 @@
       <c r="EB2" t="n">
         <v>1743026881</v>
       </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="ED2" t="n">
+      <c r="EC2" t="b">
         <v>0</v>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
       </c>
       <c r="EE2" t="inlineStr"/>
     </row>
